--- a/assets/01_mnl_news.xlsx
+++ b/assets/01_mnl_news.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\공유 드라이브\00_RyanKim_김장길\81_방송_Broadcast\10_엠엔엘_방송자료\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B23F76-B545-4DE6-A225-519F2363F59D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0AA432-E758-4BEB-BEBC-7E4B2E4C0A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4740" yWindow="4610" windowWidth="33660" windowHeight="12360" xr2:uid="{13C56ADD-2978-4209-B5B1-7D56087C6640}"/>
+    <workbookView xWindow="12810" yWindow="7680" windowWidth="20780" windowHeight="12360" xr2:uid="{13C56ADD-2978-4209-B5B1-7D56087C6640}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="371">
   <si>
     <t>구분</t>
   </si>
@@ -62,15 +62,9 @@
     <t>전국</t>
   </si>
   <si>
-    <t>2026.9.15.</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
-    <t>2026.9.14.</t>
-  </si>
-  <si>
     <t>경기</t>
   </si>
   <si>
@@ -80,33 +74,21 @@
     <t>글로벌</t>
   </si>
   <si>
-    <t>2026.9.17.</t>
-  </si>
-  <si>
     <t>서울경제진흥원</t>
   </si>
   <si>
-    <t>기술개발(R&amp;D)</t>
-  </si>
-  <si>
     <t>2026.9.30.</t>
   </si>
   <si>
     <t>서울</t>
   </si>
   <si>
-    <t>충남</t>
-  </si>
-  <si>
     <t>지원사업</t>
   </si>
   <si>
     <t>지원자격</t>
   </si>
   <si>
-    <t>2026.9.16.</t>
-  </si>
-  <si>
     <t>2026.9.28.</t>
   </si>
   <si>
@@ -119,87 +101,27 @@
     <t>2026.9.21.</t>
   </si>
   <si>
-    <t>에너지밸리기업개발원</t>
-  </si>
-  <si>
     <t>광운대학교산학협력단</t>
   </si>
   <si>
     <t>부산기술창업투자원</t>
   </si>
   <si>
-    <t>(주)엠와이소셜컴퍼니</t>
-  </si>
-  <si>
-    <t>2026년 인천국제공항공사 상생형 창업·벤처기업 지원사업 모집공고</t>
-  </si>
-  <si>
-    <t>한국표준협회</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179111</t>
-  </si>
-  <si>
-    <t>2026년 웰컴 투 팁스 3차 참가기업 모집 (동남권)</t>
-  </si>
-  <si>
-    <t>(주)로우파트너스</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179126</t>
-  </si>
-  <si>
-    <t>서울창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>2026년 스마트상점 기술보급사업 참여 소상공인 모집공고(2차)</t>
-  </si>
-  <si>
-    <t>소상공인시장진흥공단</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179106</t>
-  </si>
-  <si>
-    <t>한국여성과학기술인육성재단(WISET)</t>
-  </si>
-  <si>
     <t>2026.10.2.</t>
   </si>
   <si>
-    <t>서울핀테크랩</t>
-  </si>
-  <si>
     <t>2026.9.22.</t>
   </si>
   <si>
-    <t>2026.9.25.</t>
-  </si>
-  <si>
-    <t>2026.9.12.</t>
-  </si>
-  <si>
     <t>서울시립대학교창업보육센터</t>
   </si>
   <si>
     <t>2026.9.27.</t>
   </si>
   <si>
-    <t>관악구청</t>
-  </si>
-  <si>
-    <t>창업진흥원</t>
-  </si>
-  <si>
     <t>2026.10.14.</t>
   </si>
   <si>
-    <t>서강대학교산학협력단</t>
-  </si>
-  <si>
-    <t>2026년 9월 3주차</t>
-  </si>
-  <si>
     <t>시설·공간·보육</t>
   </si>
   <si>
@@ -209,15 +131,9 @@
     <t>(주)오픈놀</t>
   </si>
   <si>
-    <t>서울시 소재 투자 IR 희망 스타트업</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179222</t>
   </si>
   <si>
-    <t>2026 글로벌 스타트업 서밋 (일본2차) 세미나&amp;밋업 참여기업 모집</t>
-  </si>
-  <si>
     <t>인천창조경제혁신센터</t>
   </si>
   <si>
@@ -230,15 +146,9 @@
     <t>멘토링·컨설팅·교육</t>
   </si>
   <si>
-    <t>「청년창업기업·사회적경제기업·예비창업자(소상공인) 대상」 2025년 제1기 서울콜라보레이션 청년 성공창업스쿨 교육생 모집</t>
-  </si>
-  <si>
     <t>서대문구청 청년정책과</t>
   </si>
   <si>
-    <t>청년창업기업, 사회적경제기업, 예비창업자(소상공인)</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179218</t>
   </si>
   <si>
@@ -248,40 +158,15 @@
     <t>수원대학교 창업지원단</t>
   </si>
   <si>
-    <t>창업 아이템을 보유한 예비창업자</t>
-  </si>
-  <si>
-    <t>사업화지원 상위 3팀
-각 1백만원</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179214</t>
   </si>
   <si>
-    <t>AI 기반 지역관광 문제해결 프로젝트((역사문화형)) 「AAII 배리어프리 부문」공고문</t>
-  </si>
-  <si>
-    <t>한국관광공사</t>
-  </si>
-  <si>
-    <t>관광현장 문제해결 혁신기술 보유 AI 배리어프리 기업</t>
-  </si>
-  <si>
-    <t>실증비용 5,500만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179203</t>
-  </si>
-  <si>
     <t>2026년 서경대학교 창업보육센터 입주기업 모집(3차)</t>
   </si>
   <si>
     <t>서경대학교산학협력단</t>
   </si>
   <si>
-    <t>예비창업자 및 창업 7년 이내 초기 창업기업</t>
-  </si>
-  <si>
     <t>서울 성북,독립,유료</t>
   </si>
   <si>
@@ -291,161 +176,54 @@
     <t>행사·네트워크</t>
   </si>
   <si>
-    <t>경기도경제과학진흥원과 함께하는 모두의 창업(2차) 사업 설명회</t>
-  </si>
-  <si>
-    <t>(재)경기도경제과학진흥원</t>
-  </si>
-  <si>
-    <t>예비창업자 또는 업력 7년 이내 이종창업 희망기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179219</t>
-  </si>
-  <si>
-    <t>2026년 서대문구 청년창업기업 및 사회연대경제기업 수시 전문상담 경영컨설팅 신청 기업 모집 공고</t>
-  </si>
-  <si>
-    <t>서대문구 소재 대표자 39세 이하 청년창업기업, 사회연대경제기업, 예비창업자</t>
-  </si>
-  <si>
     <t>2026.11.30.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179184</t>
   </si>
   <si>
-    <t>한국기술교육대학교 오픈이노베이션 프로그램 참여기업 모집 공고</t>
-  </si>
-  <si>
     <t>한국기술교육대학교 산학협력단</t>
   </si>
   <si>
-    <t>충남 소재 신성장동력산업 분야 창업 7년 이내 기업</t>
-  </si>
-  <si>
-    <t>PoC 최대 2천만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179213</t>
-  </si>
-  <si>
     <t>창업교육</t>
   </si>
   <si>
-    <t>모두의 창업 로컬기업 육성사업 교육(동남권)</t>
-  </si>
-  <si>
-    <t>알에이치테크</t>
-  </si>
-  <si>
-    <t>로컬 예비창업자 및 기창업자 누구나</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179212</t>
-  </si>
-  <si>
     <t>2026년 대전 스타트업 원스톱 지원센터 아카데미 3회차</t>
   </si>
   <si>
     <t>주식회사 렛츠</t>
   </si>
   <si>
-    <t>대전시 소재 예비 및 창업 3년 이내 기업</t>
-  </si>
-  <si>
     <t>2026.10.25.</t>
   </si>
   <si>
-    <t>베트남 테크페스트(TECHFEST 2026) K-스타트업 통합관 참가기업 모집공고</t>
-  </si>
-  <si>
-    <t>창업 7년 이내 기업 (신산업 분야 10년 이내)</t>
-  </si>
-  <si>
-    <t>해외진출지원
-최대 150만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179192</t>
-  </si>
-  <si>
-    <t>[서초창업스테이션] 9월 1:1 전문 분야 컨설팅 - IR 덱 디자인 고도화, 세무회계</t>
-  </si>
-  <si>
-    <t>컨설팅 참여 희망 예비창업자 및 기창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179169</t>
-  </si>
-  <si>
-    <t>2026 아스트라제네카-서울바이오허브 글로벌 오픈이노베이션 참여기업 모집</t>
-  </si>
-  <si>
     <t>한국과학기술연구원</t>
   </si>
   <si>
-    <t>설립 8년 미만 바이오 분야 창업기업</t>
-  </si>
-  <si>
-    <t>연구지원금 3천만원
-한국/스웨덴 입주지원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179174</t>
-  </si>
-  <si>
     <t>[서초창업스테이션] 9월 창업 교육 - 스타트업을 위한 온라인 판로개척</t>
   </si>
   <si>
-    <t>예비창업자 및 창업 7년 이내 기업</t>
-  </si>
-  <si>
     <t>2026.9.18.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179167</t>
   </si>
   <si>
-    <t>2026년 한전KPS 창업벤처기업 육성 지원사업 참여기업 모집안내(연장)</t>
-  </si>
-  <si>
-    <t>창업 7년 미만 원자력/화력/신재생/친환경 분야 중소·벤처기업</t>
-  </si>
-  <si>
-    <t>사업화자금 1천만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179193</t>
-  </si>
-  <si>
     <t>[고양시×스타필드 고양] 2026 고양 스타트업 팝업스토어 참가기업 모집</t>
   </si>
   <si>
     <t>고양시청</t>
   </si>
   <si>
-    <t>고양시 소재 업력 7년 이내 창업기업</t>
-  </si>
-  <si>
-    <t>스타트업 판로지원</t>
-  </si>
-  <si>
     <t>2026.9.20.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179191</t>
   </si>
   <si>
-    <t>한국공학대학교 창업보육센터 입주기업 모집공고</t>
-  </si>
-  <si>
     <t>㈜한국공학대학교기술지주회사</t>
   </si>
   <si>
-    <t>예비창업자 및 창업 7년 미만 중소벤처기업</t>
-  </si>
-  <si>
     <t>경기 시흥,독립,유료</t>
   </si>
   <si>
@@ -455,9 +233,6 @@
     <t>2026년 투자 유치 역량 강화 특강</t>
   </si>
   <si>
-    <t>관내 예비창업자 및 창업 7년 미만 초기창업자</t>
-  </si>
-  <si>
     <t>2026.10.7.</t>
   </si>
   <si>
@@ -470,9 +245,6 @@
     <t>대전일자리경제진흥원</t>
   </si>
   <si>
-    <t>대전 관내 창업 희망 예비창업자</t>
-  </si>
-  <si>
     <t>대전 유성,독립,무료</t>
   </si>
   <si>
@@ -488,492 +260,42 @@
     <t>인천지방조달청</t>
   </si>
   <si>
-    <t>수도권 소재 본사 또는 공장 보유 중소기업</t>
-  </si>
-  <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179205</t>
   </si>
   <si>
-    <t>대학생 창업자가 투자를 유치하며 겪었던 이야기들(#고객이 원하는 시장을 찾는 방법) - 제9차 벤처스타트업 아카데미</t>
-  </si>
-  <si>
-    <t>창업에 관심 있는 누구나</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179202</t>
-  </si>
-  <si>
-    <t>2026년 국가철도공단 창업·벤처기업 지원사업 희망기업 모집공고</t>
-  </si>
-  <si>
-    <t>국가철도공단</t>
-  </si>
-  <si>
-    <t>창업 7년 이내 창업·벤처기업 및 예비창업자</t>
-  </si>
-  <si>
-    <t>10만원 상당
-사무용품</t>
-  </si>
-  <si>
     <t>2026.10.30.</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179209</t>
-  </si>
-  <si>
-    <t>2026년 SVC Seoul 인턴십 프로그램 학생인턴 모집공고</t>
-  </si>
-  <si>
-    <t>국내 대학 재학생, 휴학생 및 졸업 3년 이내 자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179200</t>
-  </si>
-  <si>
-    <t>2026 고양시 청년 창업가 네트워킹 및 선배 창업가 특강</t>
-  </si>
-  <si>
-    <t>고양시 내 예비, 초기 창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179185</t>
-  </si>
-  <si>
-    <t>2026년 청주미래누리터(공공지식산업센터) 입주기업 모집공고</t>
-  </si>
-  <si>
-    <t>(사)한국산업진흥협회 청주미래누리터</t>
-  </si>
-  <si>
-    <t>제조업, 지식기반산업, 정보통신산업 등 입주 가능 업종 기업</t>
-  </si>
-  <si>
-    <t>충북 청주,독립,유료</t>
-  </si>
-  <si>
     <t>충북</t>
   </si>
   <si>
     <t>2026.10.31.</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179173</t>
-  </si>
-  <si>
-    <t>모두의창업 지원서 작성법 특강 "모두의창업 지원서 작성포인트! 사례로 알려드립니다"</t>
-  </si>
-  <si>
-    <t>단국대학교</t>
-  </si>
-  <si>
-    <t>모두의창업에 관심 있는 누구나</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179162</t>
-  </si>
-  <si>
-    <t>2026년 안산정보산업진흥센터(경기TP안산창업보육센터) 제3차 신규 입주자 모집 공고</t>
-  </si>
-  <si>
-    <t>경기테크노파크</t>
-  </si>
-  <si>
-    <t>IT·SW 및 관련 기술 분야 예비창업자 및 창업 3년 이내 기업</t>
-  </si>
-  <si>
-    <t>경기 안산,독립,유료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179172</t>
-  </si>
-  <si>
-    <t>Midnight Korea Hackathon 2026 &amp; Privacy Night 참가 안내</t>
-  </si>
-  <si>
-    <t>프라이버시 기술 및 블록체인 분야 관심 기업, 개인 및 팀</t>
-  </si>
-  <si>
-    <t>시상금 총 6천달러 상당</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179179</t>
-  </si>
-  <si>
-    <t>2026 협성대학교 창업보육센터 하반기 신규 입주기업 모집 공고</t>
-  </si>
-  <si>
-    <t>협성대학교 창업보육센터</t>
-  </si>
-  <si>
-    <t>예비창업자 및 창업 7년 이내 중소기업</t>
-  </si>
-  <si>
-    <t>경기 화성,독립,유료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179178</t>
-  </si>
-  <si>
-    <t>『 2026 산림분야 오픈이노베이션 』 현대건설, 한국콜마 협력 희망 스타트업 모집(~9.30. 15:00)</t>
-  </si>
-  <si>
-    <t>산림/AI/바이오 등 수요과제 분야 창업 7년 이내 기업 (신사업 10년)</t>
-  </si>
-  <si>
     <t>오픈이노베이션</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179186</t>
-  </si>
-  <si>
-    <t>2026 LX세미콘 x 충남창조경제혁신센터 Nexus Connect 오픈이노베이션 밋업 데이</t>
-  </si>
-  <si>
-    <t>충남창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>LX세미콘 기술 수요 관련 창업 7년 이내 스타트업</t>
-  </si>
-  <si>
     <t>2026.10.6.</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179190</t>
-  </si>
-  <si>
-    <t>2026년 하반기 서울창업허브 성수 입주기업 모집</t>
-  </si>
-  <si>
-    <t>창업 7년 미만 스타트업 (신산업 10년 이내)</t>
-  </si>
-  <si>
-    <t>서울 성동,독립,유료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179187</t>
-  </si>
-  <si>
-    <t>[무료 AI 역량강화 교육]생성형 AI 기반 글로벌 무역·물류 데이터 분석 및 공급망 최적화 과정 (대전)</t>
-  </si>
-  <si>
     <t>(주)글로벌창업연구소</t>
   </si>
   <si>
-    <t>글로벌 공공조달 및 수출(예비) 기업 실무자 및 재직자</t>
-  </si>
-  <si>
     <t>2026.10.27.</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179171</t>
-  </si>
-  <si>
-    <t>2026 예비창업패키지 INU 창업준비 아카데미(1기) 교육생 모집공고</t>
-  </si>
-  <si>
-    <t>국립대학법인 인천대학교</t>
-  </si>
-  <si>
-    <t>경인권(경기·인천) 예비창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179135</t>
-  </si>
-  <si>
-    <t>SURF 2026 INCHEON (인천스타트업위크) 사전 등록 및 비즈니스 밋업 신청 오픈</t>
-  </si>
-  <si>
-    <t>비즈니스 밋업 및 멘토링 희망 스타트업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179156</t>
-  </si>
-  <si>
-    <t>성남 기후테크 UpSkill 아카데미 Vol.2 - 비즈니스모델 개발과 기술사업화</t>
-  </si>
-  <si>
-    <t>도시혁신그룹무브먼트주식회사</t>
-  </si>
-  <si>
-    <t>기후테크에 관심 있는 누구나</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179125</t>
-  </si>
-  <si>
-    <t>2026 서울AI로봇쇼 피지컬 AI 포럼 참관객 모집</t>
-  </si>
-  <si>
-    <t>피지컬 AI 및 로봇 관심 기관·기업 관계자, 연구원, 학생, 시민</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179158</t>
-  </si>
-  <si>
-    <t>호서대학교 서울창업보육센터 신규입주모집 공고</t>
-  </si>
-  <si>
-    <t>호서대학교산학협력단</t>
-  </si>
-  <si>
-    <t>예비창업자 및 창업 5년 미만 기업</t>
-  </si>
-  <si>
-    <t>서울 서초,독립,유료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179168</t>
-  </si>
-  <si>
-    <t>정책자금</t>
-  </si>
-  <si>
-    <t>2026년 패션기업 연말 맞춤형 제품 제작·프로모션 지원사업 참여기업 모집</t>
-  </si>
-  <si>
-    <t>서울 소재 중소 패션 및 라이프스타일 기업</t>
-  </si>
-  <si>
-    <t>제작지원 최대 3백만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179157</t>
-  </si>
-  <si>
-    <t>「아시아 창업 엑스포 FLY ASIA 2026」참여 스타트업 모집(1:1 밋업, 전시)</t>
-  </si>
-  <si>
-    <t>국내외 유망 스타트업</t>
-  </si>
-  <si>
     <t>2026.9.23.</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179164</t>
-  </si>
-  <si>
-    <t>2026 천안 C-STAR Awards 기술/투자 상담회 참여기업 모집</t>
-  </si>
-  <si>
-    <t>주식회사 킹고스프링</t>
-  </si>
-  <si>
-    <t>천안시 소재/예정 또는 전략산업 관련 예비 및 초기 창업기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179163</t>
-  </si>
-  <si>
-    <t>청년창업 거주지원시설(창업하여家) 입주자 3차 모집</t>
-  </si>
-  <si>
-    <t>(재)광주테크노파크</t>
-  </si>
-  <si>
-    <t>전남/광주 거주 만 39세 이하 무주택 청년 창업 3년 이내자</t>
-  </si>
-  <si>
     <t>광주 북구,독립,유료</t>
   </si>
   <si>
-    <t>전남</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179138</t>
-  </si>
-  <si>
-    <t>「글로벌 교류·투자유치 Meet Taipei 2026 통합관」 참가 기업 모집 공고</t>
-  </si>
-  <si>
-    <t>부산 소재 창업 7년 이내 기업 (신산업 10년)</t>
-  </si>
-  <si>
-    <t>해외진출지원
-최대 1백만원</t>
-  </si>
-  <si>
     <t>부산</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179160</t>
-  </si>
-  <si>
-    <t>2026 서울창업허브 공덕 9월 허브아워 - 투자, 수출 컨설팅</t>
-  </si>
-  <si>
-    <t>서울 소재 스타트업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179152</t>
-  </si>
-  <si>
-    <t>(대구센터) 2026년 제8회 제대군인 창업 워크숍 개최 안내</t>
-  </si>
-  <si>
-    <t>국가보훈부</t>
-  </si>
-  <si>
-    <t>5년 이상 중·장기복무 제대군인 및 전역 3년 이내 자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179146</t>
-  </si>
-  <si>
-    <t>2026년 바이오벤치마킹스쿨(BBS) 16기 수강자 모집</t>
-  </si>
-  <si>
-    <t>충북창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>제약·바이오 스타트업 관계자, 예비창업자 및 관심자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179145</t>
-  </si>
-  <si>
-    <t>2026 제조전문형 메이커스페이스 2차(일반/학생) 프로젝트 모집</t>
-  </si>
-  <si>
-    <t>국민대학교</t>
-  </si>
-  <si>
-    <t>시제품 아이디어를 가진 예비창업자, 창업 7년 미만, 학생</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179141</t>
-  </si>
-  <si>
-    <t>충북대학교 『글로벌(G)테크벤처센터(BI) 』 입주기업 모집</t>
-  </si>
-  <si>
-    <t>충북대학교</t>
-  </si>
-  <si>
-    <t>충북 청주,독립/공유,유료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179147</t>
-  </si>
-  <si>
-    <t>2026년 여성과학기술인 R&amp;D 경력복귀 지원사업 하반기 모집 공고</t>
-  </si>
-  <si>
-    <t>미취업 여성과학기술인(학사 이상) 및 연구기관</t>
-  </si>
-  <si>
-    <t>연구개발비
-최대 2,300만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179143</t>
-  </si>
-  <si>
-    <t>「성남하이테크밸리 복합문화센터」 (예비)창업기업 입주 모집</t>
-  </si>
-  <si>
-    <t>성남산업진흥원</t>
-  </si>
-  <si>
-    <t>예비창업자 및 창업 3년 이내 기업</t>
-  </si>
-  <si>
-    <t>경기 성남,공유,무료</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179088</t>
-  </si>
-  <si>
-    <t>구로구 청년창업지원센터 일반 창업교육(하반기: 3회차): 서울시 청년이 활용 가능한 창업지원 정책</t>
-  </si>
-  <si>
     <t>구로구 청년창업지원센터</t>
   </si>
   <si>
-    <t>19 ~ 39세 서울시 거주 청년 (예비)창업희망자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179139</t>
-  </si>
-  <si>
-    <t>2026 한·독 바이오·헬스케어 온라인 사전 세미나</t>
-  </si>
-  <si>
-    <t>일이삼팩토리</t>
-  </si>
-  <si>
-    <t>독일·유럽 진출 희망 바이오·헬스케어 기업 및 유관기관</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179124</t>
-  </si>
-  <si>
-    <t>청년 창업 인사이트 밋업</t>
-  </si>
-  <si>
-    <t>1987년 이후 출생 청년 예비 및 초기창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179134</t>
-  </si>
-  <si>
-    <t>2026 강원권 LIPS 민간운영사 연합 INVESTOR DAY 9월 참여기업 모집</t>
-  </si>
-  <si>
-    <t>재단법인 강원창조경제혁신센터</t>
-  </si>
-  <si>
-    <t>업력 1년 이상 창업기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179128</t>
-  </si>
-  <si>
-    <t>[숭실대학교 캠퍼스타운] 숭실대 캠퍼스타운 x 에네이 클라우드 AX전환 PBL과정 참여자 모집</t>
-  </si>
-  <si>
-    <t>숭실대학교산학협력단</t>
-  </si>
-  <si>
-    <t>캠퍼스타운 입주기업, AI전공자, (예비)창업기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179117</t>
-  </si>
-  <si>
-    <t>2026년 한라대학교 창업보육센터 9월 신규입주기업 모집 공고</t>
-  </si>
-  <si>
-    <t>한라대학교산학협력단</t>
-  </si>
-  <si>
-    <t>예비창업자 및 창업 7년 미만 기업</t>
-  </si>
-  <si>
-    <t>강원 원주,독립/공유,유료</t>
-  </si>
-  <si>
-    <t>강원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179123</t>
-  </si>
-  <si>
-    <t>창업 7년 이내 중소기업 또는 벤처인증 중소기업</t>
-  </si>
-  <si>
-    <t>사업화지원 1천만원</t>
-  </si>
-  <si>
-    <t>동남권(부산·울산·경남) 소재 창업 2년 3개월 미만 기업</t>
-  </si>
-  <si>
-    <t>정상 영업 중인 소상공인</t>
-  </si>
-  <si>
-    <t>스마트기술 도입지원</t>
-  </si>
-  <si>
     <t>판로·해외진출</t>
   </si>
   <si>
@@ -983,12 +305,6 @@
     <t>중소상공인희망재단</t>
   </si>
   <si>
-    <t>소상공인</t>
-  </si>
-  <si>
-    <t>부스지원</t>
-  </si>
-  <si>
     <t>2026.10.16.</t>
   </si>
   <si>
@@ -1001,169 +317,842 @@
     <t>비엑스플랜트</t>
   </si>
   <si>
-    <t>CDMO 활용 검토 및 신약개발/바이오 분야 관계자</t>
-  </si>
-  <si>
     <t>2026.10.12.</t>
   </si>
   <si>
     <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179195</t>
   </si>
   <si>
-    <t>첨단기술기업 지정 컨설팅 희망기업 모집</t>
-  </si>
-  <si>
-    <t>윕스</t>
-  </si>
-  <si>
-    <t>대덕특구 소재 중소벤처기업 중 법인세 감면 희망 기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179210</t>
-  </si>
-  <si>
-    <t>[서울과학기술대학교]레이저커팅기 장비교육</t>
-  </si>
-  <si>
-    <t>서울과학기술대학교</t>
-  </si>
-  <si>
-    <t>예비창업자 및 창업 7년 이내 초기창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179196</t>
-  </si>
-  <si>
-    <t>로컬임팩트는 왜 확장되지 않는가? | 신한금융희망재단 × 제3회 대한민국 사회적가치 페스타</t>
-  </si>
-  <si>
-    <t>신한금융희망재단 × 제3회 대한민국 사회적가치 페스타</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179176</t>
-  </si>
-  <si>
-    <t>2026년 강동 K-ISS멘토링센터 4차 교육 및 튜토링 과정 투자 유치 전략과 IR 피칭 스킬업</t>
-  </si>
-  <si>
-    <t>주식회사 이노시아</t>
-  </si>
-  <si>
-    <t>창업자 및 예비창업자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179180</t>
-  </si>
-  <si>
-    <t>앤틀러코리아 ANTLER INCEPTION 참여 기업 모집 | Build Money-making AI</t>
-  </si>
-  <si>
-    <t>Build Money-making AI</t>
-  </si>
-  <si>
-    <t>글로벌 투자연계</t>
-  </si>
-  <si>
-    <t>앤틀러코리아</t>
-  </si>
-  <si>
-    <t>2026.9.26.</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179189</t>
-  </si>
-  <si>
-    <t>2026년 서강비즈니스센터 입주기업 모집(~9/20)</t>
-  </si>
-  <si>
     <t>서울 마포,독립,유료</t>
   </si>
   <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179198</t>
-  </si>
-  <si>
-    <t>2026 고양시 F&amp;B 성장지원 프로그램 with G-ROUND 877 참여기업 모집공고</t>
-  </si>
-  <si>
-    <t>스타에셋 파트너스 주식회사</t>
-  </si>
-  <si>
-    <t>고양시 소재 F&amp;B·프랜차이즈 분야 창업 7년 이내 초기 기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179204</t>
-  </si>
-  <si>
-    <t>[2026 SK임팩트부스터 데이] SK와 스타트업이 만드는 협력의 시작점, 9/22 SK임팩트부스터 데이에 초대합니다</t>
-  </si>
-  <si>
-    <t>마크앤컴퍼니</t>
-  </si>
-  <si>
-    <t>대기업 협력 희망 스타트업, 투자자, 소셜벤처 등</t>
-  </si>
-  <si>
-    <t>2026.9.19.</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179166</t>
-  </si>
-  <si>
-    <t>2026년 청년창업기업 세무 역량강화 특강 및 1:1 멘토링 참여자 모집</t>
-  </si>
-  <si>
-    <t>(재)성동벤처밸리</t>
-  </si>
-  <si>
-    <t>만 39세 이하 청년 예비창업자 및 기창업 기업 대표자·임직원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179151</t>
-  </si>
-  <si>
-    <t>12대 국가전략기술 분야 기술이전 수요 모집</t>
-  </si>
-  <si>
-    <t>공공기술 기술이전 및 사업화를 희망하는 예비창업자 및 기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179182</t>
-  </si>
-  <si>
-    <t>K-이커머스 미국 진출의 모든 것: 크라우드펀딩부터 Shopify·글로벌 결제까지 세미나 참여기업 모집</t>
-  </si>
-  <si>
-    <t>(주)펀딩인사이더</t>
-  </si>
-  <si>
-    <t>미국 진출 및 글로벌 이커머스 관심 기업 대표 및 실무자</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179181</t>
-  </si>
-  <si>
-    <t>[모집기간 연장] 2026 현대모비스 CSV 오픈 이노베이션 참여 기업 모집</t>
-  </si>
-  <si>
-    <t>현대모비스와 PoC 가능한 혁신 기술 보유 기창업자</t>
-  </si>
-  <si>
-    <t>PoC 최대 9천만원</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179159</t>
-  </si>
-  <si>
-    <t>26년 9월 스타트업 언론 홍보 지원사업 참가사 모집 공고(1차)</t>
-  </si>
-  <si>
     <t>스타트업데일리</t>
   </si>
   <si>
-    <t>예비창업자 및 창업 7년 이내 초기 기업</t>
-  </si>
-  <si>
-    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179149</t>
+    <t>2026년 9월 4주차</t>
+  </si>
+  <si>
+    <t>「충북 제조창업 마스터 매칭 프로그램」 참여기업 모집</t>
+  </si>
+  <si>
+    <t>충북테크노파크</t>
+  </si>
+  <si>
+    <t>창업 7년 이내 H/W 제조분야 창업기업 및 예비창업자, 5개사</t>
+  </si>
+  <si>
+    <t>컨설팅지원 최대 1,800만원
+시제품제작 최대 6백만원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179288</t>
+  </si>
+  <si>
+    <t>2026 중장년기술창업센터 제3차 신규 입주기업 모집</t>
+  </si>
+  <si>
+    <t>안양산업진흥원</t>
+  </si>
+  <si>
+    <t>중장년 예비창업자 또는 창업3년이내 기업, 2개사 내외</t>
+  </si>
+  <si>
+    <t>경기 안양,공유,무료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179297</t>
+  </si>
+  <si>
+    <t>2026년 시흥창업캠프</t>
+  </si>
+  <si>
+    <t>알파브라더스</t>
+  </si>
+  <si>
+    <t>시흥시 관내 예비창업자 및 창업 7년 이내 스타트업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179272</t>
+  </si>
+  <si>
+    <t>2026년 하반기 경기도여성창업보육센터 입주기업 모집 연장공고</t>
+  </si>
+  <si>
+    <t>경기도일자리재단</t>
+  </si>
+  <si>
+    <t>경기도 내 여성 예비창업자 또는 창업3년이내 여성기업, 3개사</t>
+  </si>
+  <si>
+    <t>경기 안산,독립/공유,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179289</t>
+  </si>
+  <si>
+    <t>2026 글로컬 Angelwave IR Camp</t>
+  </si>
+  <si>
+    <t>한국엔젤투자협회</t>
+  </si>
+  <si>
+    <t>호남권(전남광주,전북,제주) 창업7년이내 로컬기업 12개사 내외</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179282</t>
+  </si>
+  <si>
+    <t>「서울소셜벤처허브」2026년 '허브 멤버스' 입주사 추가모집</t>
+  </si>
+  <si>
+    <t>서울소셜벤처허브</t>
+  </si>
+  <si>
+    <t>예비창업자(6개월내 창업예정) 또는 창업1년이내 서울 소재 기업</t>
+  </si>
+  <si>
+    <t>서울 강남,공유,유료</t>
+  </si>
+  <si>
+    <t>2026.9.29.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179270</t>
+  </si>
+  <si>
+    <t>구로구 청년창업지원센터_입주기업 모집·선발</t>
+  </si>
+  <si>
+    <t>19~39세 서울시 거주 청년창업자</t>
+  </si>
+  <si>
+    <t>서울 구로,독립,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179285</t>
+  </si>
+  <si>
+    <t>2026-11회 호남권 엔젤투자 피칭룸 in 전남광주</t>
+  </si>
+  <si>
+    <t>전남광주 소재 스타트업 및 예비창업자, 10개사 내외</t>
+  </si>
+  <si>
+    <t>2026.10.9.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179265</t>
+  </si>
+  <si>
+    <t>2026년 28청춘창업소 액셀러레이팅 프로그램 전문가 멘토링 3차</t>
+  </si>
+  <si>
+    <t>고양시 거주 예비·초기창업자 또는 고양시 소재 기업·학교 재학생</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179244</t>
+  </si>
+  <si>
+    <t>[부산대학교병원] 의료·헬스케어 스타트업 인큐베이터 국내전시회(공동관) 참가지원 모집</t>
+  </si>
+  <si>
+    <t>부산대학교병원</t>
+  </si>
+  <si>
+    <t>부산 소재 의료·헬스케어 관련 중소기업</t>
+  </si>
+  <si>
+    <t>국내전시회 참가지원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179269</t>
+  </si>
+  <si>
+    <t>ETRI 기술활용 신사업 모델 공모전</t>
+  </si>
+  <si>
+    <t>에트리홀딩스</t>
+  </si>
+  <si>
+    <t>대상기술 활용 기업 및 도메인전문성 있는 예비창업자</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179280</t>
+  </si>
+  <si>
+    <t>2026. 하반기 도봉구 외식업 창업 교육생 모집</t>
+  </si>
+  <si>
+    <t>도봉구청</t>
+  </si>
+  <si>
+    <t>외식업 예비·재창업자 10명(창업예정자 우대)</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179286</t>
+  </si>
+  <si>
+    <t>제2서울핀테크랩 민간위탁 운영기관 모집</t>
+  </si>
+  <si>
+    <t>서울특별시</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179278</t>
+  </si>
+  <si>
+    <t>「2026년 제4회 부기테크 투자쇼」투자상담회 참가기업 모집</t>
+  </si>
+  <si>
+    <t>부산 소재, 투자라운드 Pre-A 이상 투자유치 희망기업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179277</t>
+  </si>
+  <si>
+    <t>2026년 민간 산림복지 창업 아카데미[2차] 참가자 모집</t>
+  </si>
+  <si>
+    <t>한국산림복지진흥원</t>
+  </si>
+  <si>
+    <t>산림복지전문업 창업 관심 예비창업자, 70명 이내</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179276</t>
+  </si>
+  <si>
+    <t>바이오스타 2.0 예비창업자 모집 공고 및 설명회 개최</t>
+  </si>
+  <si>
+    <t>첨단바이오분야 창업 준비중인 이공계 박사학위 소지자</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179256</t>
+  </si>
+  <si>
+    <t>인력</t>
+  </si>
+  <si>
+    <t>[글로벌 인재] 2026 이공계 GKS 대학원생 산학프로젝트 및 인턴십 참여기업 모집</t>
+  </si>
+  <si>
+    <t>주식회사 메이커런스</t>
+  </si>
+  <si>
+    <t>대전·세종·충남·충북 소재 스타트업 및 중소·중견기업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179275</t>
+  </si>
+  <si>
+    <t>[인천] 2026년 IP창업존 51기 교육(모두의창업 연계과정) 모집</t>
+  </si>
+  <si>
+    <t>인천상공회의소</t>
+  </si>
+  <si>
+    <t>인천시민, (예비)창업자, 학생 등 25명 내외</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179271</t>
+  </si>
+  <si>
+    <t>취약분야 상시 컨설팅 10월 참가자 모집</t>
+  </si>
+  <si>
+    <t>강동구 청년해냄센터</t>
+  </si>
+  <si>
+    <t>예비창업자, 기창업자</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179268</t>
+  </si>
+  <si>
+    <t>2026 서울게임콘텐츠센터 게임스튜디오 신규 입주기업 모집</t>
+  </si>
+  <si>
+    <t>서울 소재 또는 이전 희망 중소 게임·e스포츠 기업, 3개사 내외</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179206</t>
+  </si>
+  <si>
+    <t>2026년 1차 홍릉벤처밸리 창업보육센터 입주기업 모집</t>
+  </si>
+  <si>
+    <t>키스트이노베이션</t>
+  </si>
+  <si>
+    <t>기술성·사업성 우수 예비창업자 또는 창업7년이내 중소벤처기업, 4개사 이내</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179215</t>
+  </si>
+  <si>
+    <t>[무료 AI 역량강화 교육]생성형 AI 기반 무역 컴플라이언스 및 관세·ESG 리스크 최적화(부산)</t>
+  </si>
+  <si>
+    <t>글로벌 공공조달 및 수출(예비)기업 실무자·중간관리자급 재직자, 25명 내외</t>
+  </si>
+  <si>
+    <t>2026.11.10.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179251</t>
+  </si>
+  <si>
+    <t>2026 Innopolis×LG Open Innovation Meet-up Day</t>
+  </si>
+  <si>
+    <t>와이앤아처(주)</t>
+  </si>
+  <si>
+    <t>연구개발특구 소재 딥테크 스타트업(LG 기술수요 연계 가능)</t>
+  </si>
+  <si>
+    <t>2026.10.8.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179250</t>
+  </si>
+  <si>
+    <t>강남구 개포동지역 ㈜오피스허브 1인 창조기업 지원센터 입주기업 모집(1인실,2인실)</t>
+  </si>
+  <si>
+    <t>오피스허브</t>
+  </si>
+  <si>
+    <t>예비창업자 및 창업7년이내 기업</t>
+  </si>
+  <si>
+    <t>서울 강남,독립,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179249</t>
+  </si>
+  <si>
+    <t>2026 홍콩 메가쇼(Mega Show Hong Kong 2026) 참가기업 모집</t>
+  </si>
+  <si>
+    <t>서울 소재 선물·가정용품 분야 중소기업</t>
+  </si>
+  <si>
+    <t>해외전시부스 참가지원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179243</t>
+  </si>
+  <si>
+    <t>2026년 초기창업패키지 로켓십 IR 경진대회 참가기업 모집(2회차: 콘텐츠·플랫폼)</t>
+  </si>
+  <si>
+    <t>씨엔티테크(주)</t>
+  </si>
+  <si>
+    <t>초기창업패키지 선정·졸업기업(콘텐츠·플랫폼분야), 창업7년미만</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179246</t>
+  </si>
+  <si>
+    <t>ICT 규제샌드박스 AI 기반 규제확인 서비스</t>
+  </si>
+  <si>
+    <t>정보통신산업진흥원</t>
+  </si>
+  <si>
+    <t>ICT 기업, 선착순 300개사</t>
+  </si>
+  <si>
+    <t>2026.12.21.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179267</t>
+  </si>
+  <si>
+    <t>2026 Silicon Valley GTM(Go-To-Market) Program - Public Announcement for Service Provider</t>
+  </si>
+  <si>
+    <t>창업진흥원 실리콘밸리사무소</t>
+  </si>
+  <si>
+    <t>2026.10.1.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179293</t>
+  </si>
+  <si>
+    <t>2026년 실리콘밸리 GTM(Go-To-Market) 프로그램 창업기업 모집</t>
+  </si>
+  <si>
+    <t>업력7년미만(신산업10년미만) 실리콘밸리 진출(예정) 창업기업, 국외창업·플립기업 포함</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179294</t>
+  </si>
+  <si>
+    <t>2027년도 초격차 스타트업 프로젝트 기술사업화 및 투자유치 주관기관 모집</t>
+  </si>
+  <si>
+    <t>중소벤처기업부</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179287</t>
+  </si>
+  <si>
+    <t>2026 대덕특구 딥테크 혁신성장 플랫폼(전략기술 발굴 및 매칭)</t>
+  </si>
+  <si>
+    <t>연구개발특구진흥재단</t>
+  </si>
+  <si>
+    <t>오픈이노베이션 운영자, 신사업 스핀오프 사업부, 스타트업·중소기업, 투자기관</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179057</t>
+  </si>
+  <si>
+    <t>2026년 튀르키예 이스탄불 식품 박람회 참가기업 모집</t>
+  </si>
+  <si>
+    <t>서울시 소재 식품 분야 중소기업</t>
+  </si>
+  <si>
+    <t>해외박람회 참가지원
+(장치비·임차비80%)</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179229</t>
+  </si>
+  <si>
+    <t>2026 투자 유치 세미나 - 투자사 관점에서 보는 투자유치를 위한 실전 전략</t>
+  </si>
+  <si>
+    <t>투자유치 전략 수립이 필요한 서울시 소재 스타트업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179224</t>
+  </si>
+  <si>
+    <t>제3회 AI 및 기술기반 창업 트렌드 세미나 참가자 모집</t>
+  </si>
+  <si>
+    <t>경기창조경제혁신센터</t>
+  </si>
+  <si>
+    <t>AI·기술창업 관심 교육관계자, 예비창업자, 대학생, 일반인</t>
+  </si>
+  <si>
+    <t>2026.10.20.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179236</t>
+  </si>
+  <si>
+    <t>2026 관악S밸리 브릿지 데모데이(S-Boost Track) 및 투자자 매칭데이 참여기업 모집</t>
+  </si>
+  <si>
+    <t>재단법인 관악중소벤처진흥원</t>
+  </si>
+  <si>
+    <t>로봇·AI·AX·딥테크 등 신산업분야, 투자단계 Pre-A~Series A 스타트업</t>
+  </si>
+  <si>
+    <t>시상금 총 900만원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179118</t>
+  </si>
+  <si>
+    <t>[도봉구청년창업센터] 제6차 스케일업 아카데미: 초기 스타트업을 위한 AI 재무관리 노하우</t>
+  </si>
+  <si>
+    <t>초기 스타트업 대표·임직원, 예비·초기창업자 24명 내외</t>
+  </si>
+  <si>
+    <t>AI재무관리</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179225</t>
+  </si>
+  <si>
+    <t>2026년 과천시 창업지원센터 보육실 입주기업 모집</t>
+  </si>
+  <si>
+    <t>과천시 창업지원센터</t>
+  </si>
+  <si>
+    <t>과천시 내 사업장 예정 예비창업자 또는 3년미만 기창업자, 다인실 3개사</t>
+  </si>
+  <si>
+    <t>경기 과천,공유,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179127</t>
+  </si>
+  <si>
+    <t>로봇 분야 예비·초기·재창업자를 위한 「창업 성장 프로그램」참가자 모집</t>
+  </si>
+  <si>
+    <t>한국로봇산업진흥원</t>
+  </si>
+  <si>
+    <t>로봇분야 예비창업자, 초기창업자(3년이내), 재창업희망자</t>
+  </si>
+  <si>
+    <t>대구,공유,무료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179233</t>
+  </si>
+  <si>
+    <t>2026년 9월 KICXUP 서울 입주기업 모집</t>
+  </si>
+  <si>
+    <t>설립7년미만 창업기업</t>
+  </si>
+  <si>
+    <t>서울 금천,공유,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179230</t>
+  </si>
+  <si>
+    <t>경기과학기술대학교 창업보육센터 입주기업 모집 7차</t>
+  </si>
+  <si>
+    <t>경기과학기술대학교 산학협력단</t>
+  </si>
+  <si>
+    <t>창업7년이내 기업 또는 예비창업자</t>
+  </si>
+  <si>
+    <t>경기 시흥,공유,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179231</t>
+  </si>
+  <si>
+    <t>2026년 과천시 지식정보타운 무상임대 입주기업(과천상상자이타워) 모집</t>
+  </si>
+  <si>
+    <t>지역관계없이 7년미만 기창업자(3개월내 과천 이전조건)</t>
+  </si>
+  <si>
+    <t>경기 과천,독립,유료</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179227</t>
+  </si>
+  <si>
+    <t>2026년 과천시 지식정보타운 무상임대 입주기업(과천크리에이션타워) 모집</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179228</t>
+  </si>
+  <si>
+    <t>연구개발특구진흥재단×대구창조경제혁신센터 「2026 이노폴리스 오픈이노베이션 밋업데이」참여기업 모집</t>
+  </si>
+  <si>
+    <t>전 연구개발특구 소재기업(연구소기업·첨단기술기업 우대)</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179223</t>
+  </si>
+  <si>
+    <t>2026 마포 청년 창업 아이디어 경진대회(MAPO NEXT STAGE)</t>
+  </si>
+  <si>
+    <t>마포청년창업취업지원센터 나루</t>
+  </si>
+  <si>
+    <t>전국 19~39세 청년, 예비 및 초기(3년이내) 창업자</t>
+  </si>
+  <si>
+    <t>시상금 총 660만원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179252</t>
+  </si>
+  <si>
+    <t>2026년 대전 스타트업스쿨 스타트업 리딩클래스(5회차)</t>
+  </si>
+  <si>
+    <t>대전창조경제혁신센터</t>
+  </si>
+  <si>
+    <t>스타트업 역량강화에 관심 있는 누구나</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179257</t>
+  </si>
+  <si>
+    <t>서울디자인런 2026 - 투자를 준비해야 할 때는?</t>
+  </si>
+  <si>
+    <t>디자인창업에 관심있는 예비·초기 창업가 및 시민</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179238</t>
+  </si>
+  <si>
+    <t>「민관협력 오픈이노베이션 지원」 '공공데이터 활용 지원' 공공기관 제안형(Top-Down) 창업기업 모집</t>
+  </si>
+  <si>
+    <t>중소기업 대표자로 창업7년이내 창업기업</t>
+  </si>
+  <si>
+    <t>오픈이노베이션
+협업지원금 최대 1억원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179232</t>
+  </si>
+  <si>
+    <t>투자자 IR미팅 희망 서울시 소재 스타트업</t>
+  </si>
+  <si>
+    <t>2026 글로벌 스타트업 서밋(일본2차) 세미나&amp;밋업 참여기업 모집</t>
+  </si>
+  <si>
+    <t>「청년창업기업·사회적경제기업·예비창업자(소상공인) 대상」 서울콜라보레이션 청년 성공창업스쿨 교육생 모집</t>
+  </si>
+  <si>
+    <t>청년창업기업, 사회적경제기업, 예비창업자(소상공인) 누구나</t>
+  </si>
+  <si>
+    <t>창업아이템 보유 예비창업자(전국 대학원생·동아리, 청년 및 일반)</t>
+  </si>
+  <si>
+    <t>사업화지원 100만원</t>
+  </si>
+  <si>
+    <t>예비창업자 또는 창업7년이내 초기창업기업, 10팀 내외</t>
+  </si>
+  <si>
+    <t>2026년 서대문구 청년창업기업 및 사회연대경제기업 수시 전문상담 경영컨설팅 신청기업 모집</t>
+  </si>
+  <si>
+    <t>대표자 39세이하 서대문구 소재 청년창업기업·사회연대경제기업·예비창업자</t>
+  </si>
+  <si>
+    <t>대전시 소재 예비 및 초기 창업기업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179211</t>
+  </si>
+  <si>
+    <t>(예비)창업자, 서초구 거주자·소재기업 우대, 15명</t>
+  </si>
+  <si>
+    <t>고양시 소재 업력7년이내 창업기업, 15개사</t>
+  </si>
+  <si>
+    <t>팝업스토어 참가지원</t>
+  </si>
+  <si>
+    <t>한국공학대학교 창업보육센터 입주기업 모집</t>
+  </si>
+  <si>
+    <t>예비창업자(입주후6개월내 창업) 및 창업7년미만 중소벤처기업</t>
+  </si>
+  <si>
+    <t>관내(동대문구) 예비·초기창업자</t>
+  </si>
+  <si>
+    <t>대전 관내 창업희망 예비창업자, 6개팀 내외</t>
+  </si>
+  <si>
+    <t>수도권 소재 공공조달시장 관심기업(사회적기업·장애인기업 우대), 50개사</t>
+  </si>
+  <si>
+    <t>[온라인] AI로 나만의 수익 사이트 만들기｜바이브코딩 실전 클래스</t>
+  </si>
+  <si>
+    <t>스쿨모아</t>
+  </si>
+  <si>
+    <t>온라인창업 준비 예비창업자, 1인사업자, 프리랜서, 강사, 크리에이터</t>
+  </si>
+  <si>
+    <t>2026.12.31.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=178967</t>
+  </si>
+  <si>
+    <t>블루포인트파트너스 CSprint 1기 사업가형 인재 모집</t>
+  </si>
+  <si>
+    <t>㈜블루포인트파트너스</t>
+  </si>
+  <si>
+    <t>사업가형 인재(실무경험 우대), 지역·연령제한 없음</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179274</t>
+  </si>
+  <si>
+    <t>제7회 원주권 스타트업 커뮤니티 데이 참가자 모집</t>
+  </si>
+  <si>
+    <t>상지대학교산학협력단</t>
+  </si>
+  <si>
+    <t>창업에 관심있는 누구나</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179273</t>
+  </si>
+  <si>
+    <t>2026년 제6회 SDGs 소셜벤처 챔피언십 참가자 모집</t>
+  </si>
+  <si>
+    <t>사단법인 한국지속가능소셜벤처협회</t>
+  </si>
+  <si>
+    <t>개인 또는 5인이하 팀(예비창업가·창업가·크리에이터 섹션)</t>
+  </si>
+  <si>
+    <t>시상금 총 500만원</t>
+  </si>
+  <si>
+    <t>2026.10.26.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179241</t>
+  </si>
+  <si>
+    <t>(재)여성기업종합지원센터 광주센터 BI 입주기업 모집</t>
+  </si>
+  <si>
+    <t>(재)여성기업종합지원센터 광주센터</t>
+  </si>
+  <si>
+    <t>예비 여성창업자 또는 창업7년이내 여성기업, 1개사</t>
+  </si>
+  <si>
+    <t>전남·광주</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179248</t>
+  </si>
+  <si>
+    <t>2026 서강리더스포럼 「세상을 바꾸는 질문」</t>
+  </si>
+  <si>
+    <t>서강대학교</t>
+  </si>
+  <si>
+    <t>창업관심 대학(원)생 및 예비창업자</t>
+  </si>
+  <si>
+    <t>2026.12.7.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179207</t>
+  </si>
+  <si>
+    <t>[임팩트스퀘어] 롯데케미칼 자원순환 스타트업 지원 프로그램 '프로젝트루프소셜 5기' 모집</t>
+  </si>
+  <si>
+    <t>임팩트스퀘어</t>
+  </si>
+  <si>
+    <t>재생원료·재생친화 제품 개발·사업화 기업(스타트업,벤처,사회적기업)</t>
+  </si>
+  <si>
+    <t>우수기업상금 최대 2천만원
+사업화지원금 1,500만원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179242</t>
+  </si>
+  <si>
+    <t>[창업보육센터]K-Tech 창업성장아카데미 교육프로그램 수강생 모집(~11월)</t>
+  </si>
+  <si>
+    <t>예비창업자, 전국 BI센터 입주기업, 청년창업사관학교 등 관련자, 임직원</t>
+  </si>
+  <si>
+    <t>2026.11.27.</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179208</t>
+  </si>
+  <si>
+    <t>2026년 특허출원·등록 비용 바우처 지원사업 13차(하반기 6차)</t>
+  </si>
+  <si>
+    <t>(사)한국중소기업발전협회</t>
+  </si>
+  <si>
+    <t>스타트업, 중소기업, 1인기업, 예비창업자 등</t>
+  </si>
+  <si>
+    <t>특허등록비용 지원(1건)</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179226</t>
+  </si>
+  <si>
+    <t>26년 9월 스타트업 언론 홍보 지원사업 참가사 모집 공고(2차)</t>
+  </si>
+  <si>
+    <t>예비창업자 또는 창업7년이내 초기기업</t>
+  </si>
+  <si>
+    <t>언론홍보 지원</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179255</t>
+  </si>
+  <si>
+    <t>[와이앤아처] 대기업·공공기관 신규 판로 개척 기업 상시 모집</t>
+  </si>
+  <si>
+    <t>대기업·중견기업 또는 공공기관 계약실적 보유 B2B·B2G 기업</t>
+  </si>
+  <si>
+    <t>대기업·공공기관 판로연계</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179258</t>
+  </si>
+  <si>
+    <t>2026 정주영 창업경진대회: 무한(INFINITE)</t>
+  </si>
+  <si>
+    <t>아산나눔재단</t>
+  </si>
+  <si>
+    <t>피칭 관람 및 참가에 관심있는 누구나</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179245</t>
+  </si>
+  <si>
+    <t>OCEAN'S TAP 해양 OI 리버스피칭 및 OI 밋업 참여기업 모집</t>
+  </si>
+  <si>
+    <t>탭엔젤파트너스</t>
+  </si>
+  <si>
+    <t>해양·조선 및 관련산업 기술·제품·서비스 보유 기업</t>
+  </si>
+  <si>
+    <t>https://www.k-startup.go.kr/web/contents/bizpbanc-ongoing.do?schM=view&amp;pbancSn=179259</t>
+  </si>
+  <si>
+    <t>소상공인(사업자등록 보유)</t>
+  </si>
+  <si>
+    <t>전시부스 참가지원</t>
+  </si>
+  <si>
+    <t>CDMO 활용 검토기업, 첨단바이오의약품 개발기업 등</t>
   </si>
 </sst>
 </file>
@@ -1596,7 +1585,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1611,13 +1600,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
@@ -1637,437 +1626,437 @@
     </row>
     <row r="3" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="123" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="I6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="2">
-        <v>3</v>
+        <v>120</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>90</v>
+        <v>133</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
@@ -2075,13 +2064,13 @@
         <v>0</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>2</v>
@@ -2099,146 +2088,146 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" s="2">
-        <v>2</v>
+        <v>163</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A20" s="3" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>129</v>
+        <v>8</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="I20" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>168</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="2">
-        <v>2</v>
+        <v>172</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="41" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>143</v>
+        <v>178</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>145</v>
+        <v>14</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -2246,292 +2235,292 @@
     </row>
     <row r="24" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A24" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="123" x14ac:dyDescent="0.45">
+        <v>183</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="I26" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>9</v>
+        <v>194</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>9</v>
+        <v>196</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="A28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="G28" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>171</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I29" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>205</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="41" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>176</v>
+        <v>210</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="123" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>120</v>
+        <v>213</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I31" s="2">
-        <v>2</v>
+        <v>214</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>43</v>
+        <v>212</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>184</v>
+        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>48</v>
+        <v>133</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I32" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>217</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="I33" s="2">
-        <v>2</v>
+        <v>220</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.45">
@@ -2539,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>2</v>
@@ -2563,407 +2552,407 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
-      <c r="A36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="D36" s="3" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="I36" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>202</v>
+        <v>8</v>
       </c>
       <c r="F37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="I37" s="2">
+      <c r="G39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I39" s="2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
-      <c r="A38" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A40" s="3" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>9</v>
+        <v>244</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>245</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>250</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A42" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>9</v>
+        <v>255</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="I43" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A44" s="3" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>15</v>
+        <v>261</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>232</v>
+        <v>264</v>
       </c>
       <c r="I44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>233</v>
+        <v>265</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>29</v>
+        <v>247</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>234</v>
+        <v>266</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>9</v>
+        <v>267</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>268</v>
+      </c>
+      <c r="I45" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A46" s="3" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>9</v>
+        <v>267</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="I46" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="A47" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="B47" s="1" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="I47" s="2">
-        <v>2</v>
+        <v>273</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>29</v>
+        <v>275</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>250</v>
+        <v>7</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
@@ -2971,31 +2960,31 @@
     </row>
     <row r="49" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>15</v>
+        <v>280</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.45">
@@ -3003,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>2</v>
@@ -3029,437 +3018,437 @@
     </row>
     <row r="51" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A51" s="3" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>256</v>
+        <v>30</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="123" x14ac:dyDescent="0.45">
       <c r="A52" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>9</v>
+        <v>289</v>
+      </c>
+      <c r="I52" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A53" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>263</v>
+        <v>29</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>264</v>
+        <v>30</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>266</v>
+        <v>31</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A54" s="3" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>268</v>
+        <v>32</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>119</v>
+        <v>33</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>269</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="I54" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>34</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="123" x14ac:dyDescent="0.45">
       <c r="A55" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>273</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I55" s="2">
-        <v>3</v>
+        <v>37</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A56" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>275</v>
+        <v>38</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>276</v>
+        <v>39</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>279</v>
+        <v>40</v>
       </c>
       <c r="I56" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I57" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
-      <c r="A57" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A58" s="3" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>285</v>
+        <v>36</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>287</v>
+        <v>47</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A59" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>288</v>
+        <v>50</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A60" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>291</v>
+        <v>54</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>292</v>
+        <v>30</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>294</v>
+        <v>56</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A61" s="3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>295</v>
+        <v>57</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>296</v>
+        <v>58</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>9</v>
+        <v>303</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>9</v>
+        <v>60</v>
+      </c>
+      <c r="I61" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A62" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>300</v>
+        <v>61</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>302</v>
+        <v>62</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>303</v>
+        <v>9</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>304</v>
+        <v>63</v>
       </c>
       <c r="I62" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" ht="41" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I63" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="41" x14ac:dyDescent="0.45">
       <c r="A64" s="3" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>307</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>9</v>
+        <v>71</v>
+      </c>
+      <c r="I64" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A65" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>308</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I65" s="2">
-        <v>1</v>
+        <v>74</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.45">
@@ -3467,13 +3456,13 @@
         <v>0</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>2</v>
@@ -3491,154 +3480,154 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="E67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="I67" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G67" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="I67" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="41" x14ac:dyDescent="0.45">
-      <c r="A68" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B68" s="1" t="s">
+      <c r="E68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="I68" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G68" s="4" t="s">
+      <c r="D69" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="41" x14ac:dyDescent="0.45">
-      <c r="A69" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A70" s="3" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="I70" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="H70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
-      <c r="A71" s="3" t="s">
+      <c r="D71" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E71" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="G71" s="4" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+      <c r="I71" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A72" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>333</v>
@@ -3650,280 +3639,280 @@
         <v>335</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>23</v>
+        <v>336</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
       <c r="A73" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D73" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="G73" s="4" t="s">
-        <v>341</v>
+        <v>191</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>342</v>
       </c>
       <c r="I73" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="82" x14ac:dyDescent="0.45">
       <c r="A74" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>343</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>344</v>
+        <v>8</v>
       </c>
       <c r="F74" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="A75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G74" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="I74" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="82" x14ac:dyDescent="0.45">
-      <c r="A75" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="G75" s="4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="123" x14ac:dyDescent="0.45">
+        <v>351</v>
+      </c>
+      <c r="I75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A76" s="3" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>351</v>
+        <v>96</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>9</v>
+        <v>354</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>353</v>
+        <v>13</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>355</v>
+      </c>
+      <c r="I76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A77" s="3" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>356</v>
+        <v>189</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>357</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>9</v>
+        <v>358</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>8</v>
+        <v>312</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="41" x14ac:dyDescent="0.45">
+        <v>359</v>
+      </c>
+      <c r="I77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A78" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>323</v>
+        <v>361</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="102.5" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A79" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="82" x14ac:dyDescent="0.45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
       <c r="A80" s="3" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>366</v>
+        <v>87</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>7</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>369</v>
+        <v>90</v>
       </c>
       <c r="I80" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="61.5" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="41" x14ac:dyDescent="0.45">
       <c r="A81" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>372</v>
-      </c>
       <c r="E81" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>373</v>
+        <v>94</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
